--- a/backend/src/scrapers/availity/config/Payer_mapping_ava.xlsx
+++ b/backend/src/scrapers/availity/config/Payer_mapping_ava.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Automation_Projects\Claim_Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alamelu\Documents\Repos\claim-status-check\backend\src\scrapers\availity\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF5FA72-8726-44D2-83CF-60C6AC01FB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F17329-0A11-4F70-A1B4-7FDD1D18E3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4DE94660-A54E-46F6-AD6A-893CA67AF137}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t xml:space="preserve">Payer name in excel </t>
   </si>
@@ -52,6 +52,18 @@
   </si>
   <si>
     <t>BLUE CROSS MEDICARE ADVANTAGE</t>
+  </si>
+  <si>
+    <t>Wellpoint</t>
+  </si>
+  <si>
+    <t>WELLPOINT</t>
+  </si>
+  <si>
+    <t>WellCare</t>
+  </si>
+  <si>
+    <t>WELLCARE</t>
   </si>
 </sst>
 </file>
@@ -403,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88755D1-98D7-4BD5-87AA-1A7D67B6D9D9}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -450,6 +462,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
